--- a/Excel/9. Date/Date.xlsx
+++ b/Excel/9. Date/Date.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\topna\OneDrive\Desktop\All\Unedited Excel Videos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Weekend\Excel\9. Date\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4174CEA-430F-45C0-A501-B0CC5BE6DC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D946CA-45A2-4EFB-BD90-9271C5882152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -486,25 +486,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.5546875" customWidth="1"/>
     <col min="5" max="5" width="23.77734375" customWidth="1"/>
+    <col min="6" max="6" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2">
         <f ca="1">TODAY()</f>
-        <v>45545</v>
+        <v>45850</v>
       </c>
       <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="2">
+        <f ca="1">TODAY()</f>
+        <v>45850</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -516,8 +521,12 @@
         <f>DATE(2023,12,1)</f>
         <v>45261</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="2">
+        <f>DATE(2023,7,12)</f>
+        <v>45119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -529,8 +538,12 @@
         <f>DAY(E2)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <f>DAY(F2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -542,8 +555,12 @@
         <f>MONTH(E2)</f>
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <f>MONTH(D2)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -555,8 +572,16 @@
         <f>YEAR(E2)</f>
         <v>2023</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <f ca="1">YEAR(F1)</f>
+        <v>2025</v>
+      </c>
+      <c r="G5">
+        <f>YEAR(F2)</f>
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -569,7 +594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -577,8 +602,12 @@
         <f>_xlfn.DAYS(D2,E2)</f>
         <v>284</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <f>WEEKDAY(F2,1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -586,11 +615,19 @@
         <f>_xlfn.DAYS(DATE(2027,12,1),DATE(2025,1,1))</f>
         <v>1064</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <f ca="1">_xlfn.DAYS(F1,F2)</f>
+        <v>731</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D9" s="3">
         <f ca="1">NOW()</f>
-        <v>45545.412974768522</v>
+        <v>45850.569804050923</v>
+      </c>
+      <c r="E9" s="3">
+        <f ca="1">NOW()</f>
+        <v>45850.569804050923</v>
       </c>
     </row>
   </sheetData>
